--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>victor.soares.silva27@escola.pr.gov.br</t>
+          <t>victor.soares.silva27@enscola.pr.gov.br</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
